--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,108 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ask ChatGPT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>H100-hyperscaler</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>A100-hyperscaler</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>B200</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>B300</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MI300X</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>H200</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LLM Token</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Open LLM</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Proprietary LLM</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>GDDR6</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>19.36</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,6 +535,49 @@
         <v>2.25</v>
       </c>
       <c r="M2" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M3" t="n">
         <v>19.36</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,11 @@
           <t>GDDR6</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -537,6 +542,7 @@
       <c r="M2" t="n">
         <v>19.36</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,9 +550,7 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2.83</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>7.15</v>
       </c>
@@ -579,6 +583,9 @@
       </c>
       <c r="M3" t="n">
         <v>19.36</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Ask ChatGPT</t>
+          <t>H100</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -492,100 +492,413 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>GDDR6</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>H100</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.43</v>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.98</v>
+        <v>0.9536</v>
       </c>
       <c r="K2" t="n">
-        <v>0.47</v>
+        <v>0.4726</v>
       </c>
       <c r="L2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M2" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>2.2018</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.78</v>
+      </c>
       <c r="C3" t="n">
-        <v>7.15</v>
+        <v>7.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="E3" t="n">
         <v>3.76</v>
       </c>
       <c r="F3" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9554</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.2035</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.2075</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19.31</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.2044</v>
+      </c>
+      <c r="M5" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4737</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.2315</v>
+      </c>
+      <c r="M6" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.2474</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F8" t="n">
         <v>5.93</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G8" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.2486</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G11" t="n">
         <v>6.67</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H11" t="n">
         <v>2.64</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I11" t="n">
         <v>3.44</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J11" t="n">
         <v>0.97</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K11" t="n">
         <v>0.47</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L11" t="n">
         <v>2.27</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M11" t="n">
         <v>19.36</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.83</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -476,22 +476,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>GDDR6</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>LLM Token</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Open LLM</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Proprietary LLM</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>GDDR6</t>
         </is>
       </c>
     </row>
@@ -509,16 +509,16 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.9536</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.4726</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>2.2018</v>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,16 +551,16 @@
         <v>3.33</v>
       </c>
       <c r="J3" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.9554</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.4721</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2.2035</v>
-      </c>
-      <c r="M3" t="n">
-        <v>19.31</v>
       </c>
     </row>
     <row r="4">
@@ -594,16 +594,16 @@
         <v>3.3</v>
       </c>
       <c r="J4" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.9762</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.4709</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2.2075</v>
-      </c>
-      <c r="M4" t="n">
-        <v>19.31</v>
       </c>
     </row>
     <row r="5">
@@ -637,16 +637,16 @@
         <v>3.29</v>
       </c>
       <c r="J5" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.9853</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.4698</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2.2044</v>
-      </c>
-      <c r="M5" t="n">
-        <v>19.36</v>
       </c>
     </row>
     <row r="6">
@@ -680,16 +680,16 @@
         <v>3.32</v>
       </c>
       <c r="J6" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.9931</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.4737</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>2.2315</v>
-      </c>
-      <c r="M6" t="n">
-        <v>19.36</v>
       </c>
     </row>
     <row r="7">
@@ -723,16 +723,16 @@
         <v>3.34</v>
       </c>
       <c r="J7" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.9831</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.4716</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2.2474</v>
-      </c>
-      <c r="M7" t="n">
-        <v>19.36</v>
       </c>
     </row>
     <row r="8">
@@ -766,16 +766,16 @@
         <v>3.39</v>
       </c>
       <c r="J8" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.9792</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.4683</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>2.2486</v>
-      </c>
-      <c r="M8" t="n">
-        <v>19.36</v>
       </c>
     </row>
     <row r="9">
@@ -808,12 +808,12 @@
       <c r="I9" t="n">
         <v>3.43</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>19.36</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>19.36</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -846,16 +846,16 @@
         <v>3.43</v>
       </c>
       <c r="J10" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.98</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.47</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>2.25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>19.36</v>
       </c>
     </row>
     <row r="11">
@@ -889,16 +889,16 @@
         <v>3.44</v>
       </c>
       <c r="J11" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.97</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.47</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2.27</v>
-      </c>
-      <c r="M11" t="n">
-        <v>19.36</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -436,62 +436,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>H100</t>
+          <t>H100 (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>H100-hyperscaler</t>
+          <t>H100-hyperscaler (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>A100</t>
+          <t>A100 (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>A100-hyperscaler</t>
+          <t>A100-hyperscaler (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>B200</t>
+          <t>B200 (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>B300</t>
+          <t>B300 (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MI300X</t>
+          <t>MI300X (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>H200</t>
+          <t>H200 (USD / GPU-hour)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>GDDR6</t>
+          <t>GDDR6 (USD / GB)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>LLM Token</t>
+          <t>LLM Token (USD / M tokens)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Open LLM</t>
+          <t>Open LLM (USD / M tokens)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Proprietary LLM</t>
+          <t>Proprietary LLM (USD / M tokens)</t>
         </is>
       </c>
     </row>
@@ -510,14 +510,20 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.4726</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2.2018</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -526,41 +532,65 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="J3" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.9554</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.4721</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.2035</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6.84</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>19.31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -569,41 +599,65 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.9762</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.4709</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2.2075</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7.16</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>19.31</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -612,41 +666,65 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="J5" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9853</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.4698</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.2044</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5.87</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -655,41 +733,65 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="J6" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9931</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.4737</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2.2315</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -698,41 +800,65 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9831</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.4716</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.2474</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6.69</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -741,41 +867,65 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="J8" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.9792</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.4683</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2.2486</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -784,32 +934,50 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="J9" t="n">
-        <v>19.36</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -821,41 +989,65 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C10" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.25</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -864,41 +1056,65 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="F11" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="J11" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.27</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1117,6 +1117,73 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7.16</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19.36</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1184,73 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,6 +1251,73 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5.95</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6.65</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1318,6 +1318,73 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6.77</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,6 +1385,73 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,6 +1452,73 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,73 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1586,6 +1586,65 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,6 +1645,53 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19.48</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1692,73 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6.14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,6 +1759,73 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>6.29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1826,6 +1826,73 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,6 +1893,73 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,6 +1960,73 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,73 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6.63</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>7.52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2094,73 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>19.61</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2161,6 +2161,73 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>19.61</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2228,6 +2228,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6.47</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19.61</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2295,6 +2295,73 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>19.61</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
